--- a/data/trans_orig/IP09C_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP09C_R-Habitat-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>43,85%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>6732</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11071</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -1675,47 +1675,47 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5268</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>21,07%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5256</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>21,02%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>539</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>595</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>12224</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>12471</t>
+          <t>12427</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>22715</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>58,8%</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2240,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9251</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15179</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>451</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>729</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>765</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>720</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>850</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -3795,12 +3795,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11004</t>
+          <t>10898</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>12585</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>11589</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20963</t>
+          <t>22061</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>53,59%</t>
         </is>
       </c>
     </row>
@@ -3908,12 +3908,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3978,12 +3978,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>795</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -4134,12 +4134,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>778</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>708</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>10746</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>12558</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -4477,12 +4477,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>14324</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12733</t>
+          <t>13569</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>23747</t>
+          <t>23691</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>16414</t>
+          <t>16143</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>27281</t>
+          <t>27308</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4738,12 +4738,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>23432</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>36292</t>
+          <t>35878</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>41779</t>
+          <t>43160</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>59183</t>
+          <t>61515</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -4816,12 +4816,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>13147</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>14568</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>28048</t>
+          <t>28061</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -4929,12 +4929,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>16447</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>23354</t>
+          <t>23252</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>11128</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>17347</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>638</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12698</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,66%</t>
         </is>
       </c>
     </row>
@@ -5617,62 +5617,62 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5580</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17,6%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>44,19%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5192</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>17,6%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3039</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>41,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3542</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>751</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>13787</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>44,98%</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>765</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>759</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11705</t>
+          <t>11589</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -6751,12 +6751,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13963</t>
+          <t>13795</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>9916</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19558</t>
+          <t>19561</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>18931</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>31267</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -6977,12 +6977,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>598</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6992,12 +6992,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7062,12 +7062,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>667</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7355,12 +7355,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>10730</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>491</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -7659,12 +7659,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14967</t>
+          <t>15253</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25466</t>
+          <t>25479</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,93%</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -7885,12 +7885,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -7998,12 +7998,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>481</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10134</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -8228,12 +8228,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>730</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6576</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>12453</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8411,12 +8411,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8524,12 +8524,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6590</t>
+          <t>6896</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -8567,12 +8567,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15447</t>
+          <t>15516</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8602,12 +8602,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11194</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8637,12 +8637,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13097</t>
+          <t>13373</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>24601</t>
+          <t>24353</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -8715,12 +8715,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>789</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8750,12 +8750,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>759</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8828,12 +8828,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8863,12 +8863,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>11044</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -8906,12 +8906,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>600</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8921,12 +8921,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8941,12 +8941,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8976,12 +8976,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -9136,12 +9136,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>23192</t>
+          <t>23688</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9206,12 +9206,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>20746</t>
+          <t>20142</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>36584</t>
+          <t>36724</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -9249,12 +9249,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>9332</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9284,12 +9284,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9319,12 +9319,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15991</t>
+          <t>16481</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -9362,12 +9362,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9397,12 +9397,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9432,12 +9432,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -9475,12 +9475,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>29189</t>
+          <t>29281</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>43768</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9490,12 +9490,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>29455</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>45289</t>
+          <t>43877</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9545,12 +9545,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>62877</t>
+          <t>63055</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>83887</t>
+          <t>84468</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,45%</t>
         </is>
       </c>
     </row>
@@ -9588,12 +9588,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9623,12 +9623,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>20688</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -9701,12 +9701,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>12325</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9736,12 +9736,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>16380</t>
+          <t>17248</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>25007</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -9814,12 +9814,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>28019</t>
+          <t>27791</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -10311,12 +10311,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10326,12 +10326,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10361,12 +10361,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,58%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>539</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10630,12 +10630,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10650,12 +10650,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10685,12 +10685,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10700,12 +10700,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>55,13%</t>
         </is>
       </c>
     </row>
@@ -10733,7 +10733,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -10841,12 +10841,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10856,12 +10856,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>526</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10891,12 +10891,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,64%</t>
         </is>
       </c>
     </row>
@@ -11184,12 +11184,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>7469</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11219,12 +11219,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11254,12 +11254,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11531</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11367,12 +11367,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>545</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11382,12 +11382,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -11523,12 +11523,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11538,12 +11538,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11573,12 +11573,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17626</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,96%</t>
         </is>
       </c>
     </row>
@@ -11636,12 +11636,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11651,12 +11651,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>451</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12177,12 +12177,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12338,7 +12338,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -12431,12 +12431,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12446,12 +12446,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>606</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10489</t>
+          <t>10443</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,87%</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12584,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12677,7 +12677,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12697,7 +12697,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12727,12 +12727,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>473</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12742,12 +12742,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -12775,7 +12775,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12840,12 +12840,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>583</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12855,12 +12855,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -13000,12 +13000,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13015,12 +13015,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13050,12 +13050,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13085,12 +13085,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>54,87%</t>
         </is>
       </c>
     </row>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>5049</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>741</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13276,12 +13276,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>785</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13311,12 +13311,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -13339,12 +13339,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>769</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13354,12 +13354,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13374,12 +13374,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13389,12 +13389,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13424,12 +13424,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>50,17%</t>
         </is>
       </c>
     </row>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -13585,7 +13585,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -13683,7 +13683,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -13718,7 +13718,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -13733,7 +13733,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -13908,12 +13908,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>12843</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13923,12 +13923,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>16187</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13958,12 +13958,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>25435</t>
+          <t>26336</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13993,12 +13993,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -14021,12 +14021,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>515</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14036,12 +14036,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14091,12 +14091,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14106,12 +14106,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -14134,12 +14134,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14149,12 +14149,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14169,12 +14169,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14184,12 +14184,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14204,12 +14204,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>13914</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14219,12 +14219,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -14247,12 +14247,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>11746</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>22045</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14262,12 +14262,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14282,12 +14282,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>19624</t>
+          <t>19072</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14297,12 +14297,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>23926</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>39079</t>
+          <t>37755</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14332,12 +14332,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -14360,12 +14360,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14375,12 +14375,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14395,12 +14395,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14410,12 +14410,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14430,12 +14430,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14445,12 +14445,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -14473,12 +14473,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14488,12 +14488,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14523,12 +14523,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14543,12 +14543,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>19165</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14636,12 +14636,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14656,12 +14656,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14671,12 +14671,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
